--- a/grupos/2BLCM - Estadisticos 20232.xlsx
+++ b/grupos/2BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -215,33 +215,33 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -254,18 +254,27 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AMARO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>ARRIETA</t>
   </si>
   <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
     <t>BORBONIO</t>
   </si>
   <si>
@@ -278,12 +287,6 @@
     <t>CERON</t>
   </si>
   <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -296,48 +299,30 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>IXTLA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>MAY</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MARIN</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -347,16 +332,22 @@
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
     <t>TENORIO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VOTE</t>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>NAVA</t>
@@ -371,9 +362,6 @@
     <t>MONTERROSA</t>
   </si>
   <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
     <t>HILARIO</t>
   </si>
   <si>
@@ -389,36 +377,21 @@
     <t>ZOPIYACTLE</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>DECTOR</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>VIDAL</t>
   </si>
   <si>
     <t>ARCOS</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>MANZANO</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
     <t>MIXCOA</t>
   </si>
   <si>
@@ -431,21 +404,27 @@
     <t>SALINAS</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>CAMILO</t>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
   </si>
   <si>
     <t>IRMA GUADALUPE</t>
   </si>
   <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
     <t>BRENDA</t>
   </si>
   <si>
@@ -458,12 +437,6 @@
     <t>PAOLA</t>
   </si>
   <si>
-    <t>JULIO EDUARDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
     <t>JULIAN DAVID</t>
   </si>
   <si>
@@ -485,9 +458,6 @@
     <t>TATIANA</t>
   </si>
   <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
     <t>KENIA PAOLA</t>
   </si>
   <si>
@@ -497,39 +467,24 @@
     <t>MELANY</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
     <t>MIRIAM NEFTALI</t>
   </si>
   <si>
     <t>CINTHIA</t>
   </si>
   <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
     <t>ANGEL URIEL</t>
   </si>
   <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
     <t>MICHELLE</t>
   </si>
   <si>
     <t>AXEL</t>
   </si>
   <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
     <t>LEYLA SARAI</t>
   </si>
   <si>
@@ -539,13 +494,7 @@
     <t>NOELIA</t>
   </si>
   <si>
-    <t>ABRIL AMAYRANI</t>
-  </si>
-  <si>
     <t>VERONICA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1035,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -1098,7 +1047,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1110,31 +1059,31 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -1164,22 +1113,22 @@
         <v>-1</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF4">
         <v>5</v>
       </c>
       <c r="AG4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AI4">
         <v>5</v>
@@ -1188,7 +1137,7 @@
         <v>-1</v>
       </c>
       <c r="AK4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1199,7 +1148,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -1211,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -1223,31 +1172,31 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1280,7 +1229,7 @@
         <v>5</v>
       </c>
       <c r="AD5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE5">
         <v>5</v>
@@ -1292,10 +1241,10 @@
         <v>5</v>
       </c>
       <c r="AH5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AI5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ5">
         <v>-1</v>
@@ -1312,7 +1261,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -1324,7 +1273,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -1336,31 +1285,31 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1393,10 +1342,10 @@
         <v>10</v>
       </c>
       <c r="AD6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <v>10</v>
@@ -1405,10 +1354,10 @@
         <v>10</v>
       </c>
       <c r="AH6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ6">
         <v>-1</v>
@@ -1425,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -1437,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -1449,31 +1398,31 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1506,7 +1455,7 @@
         <v>6</v>
       </c>
       <c r="AD7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE7">
         <v>7</v>
@@ -1518,16 +1467,16 @@
         <v>8</v>
       </c>
       <c r="AH7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AI7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ7">
         <v>-1</v>
       </c>
       <c r="AK7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1538,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1550,7 +1499,7 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -1562,31 +1511,31 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1616,22 +1565,22 @@
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
       <c r="AG8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI8">
         <v>9</v>
@@ -1640,7 +1589,7 @@
         <v>-1</v>
       </c>
       <c r="AK8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1651,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -1663,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -1675,31 +1624,31 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1732,7 +1681,7 @@
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AE9">
         <v>10</v>
@@ -1744,16 +1693,16 @@
         <v>10</v>
       </c>
       <c r="AH9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AI9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ9">
         <v>-1</v>
       </c>
       <c r="AK9">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1764,7 +1713,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1776,7 +1725,7 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>10</v>
@@ -1788,31 +1737,31 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1842,13 +1791,13 @@
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF10">
         <v>9</v>
@@ -1857,7 +1806,7 @@
         <v>10</v>
       </c>
       <c r="AH10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI10">
         <v>10</v>
@@ -1877,7 +1826,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -1889,7 +1838,7 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -1901,31 +1850,31 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1955,22 +1904,22 @@
         <v>-1</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11">
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI11">
         <v>7</v>
@@ -1979,7 +1928,7 @@
         <v>-1</v>
       </c>
       <c r="AK11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1990,7 +1939,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -2002,7 +1951,7 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -2014,31 +1963,31 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -2071,7 +2020,7 @@
         <v>5</v>
       </c>
       <c r="AD12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE12">
         <v>5</v>
@@ -2080,10 +2029,10 @@
         <v>5</v>
       </c>
       <c r="AG12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AI12">
         <v>5</v>
@@ -2092,7 +2041,7 @@
         <v>-1</v>
       </c>
       <c r="AK12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2103,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <v>9</v>
@@ -2115,7 +2064,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -2127,31 +2076,31 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -2184,7 +2133,7 @@
         <v>8</v>
       </c>
       <c r="AD13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE13">
         <v>9</v>
@@ -2196,16 +2145,16 @@
         <v>10</v>
       </c>
       <c r="AH13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ13">
         <v>-1</v>
       </c>
       <c r="AK13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2216,7 +2165,7 @@
         <v>4</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -2228,7 +2177,7 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -2240,31 +2189,31 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2294,10 +2243,10 @@
         <v>-1</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE14">
         <v>5</v>
@@ -2309,7 +2258,7 @@
         <v>5</v>
       </c>
       <c r="AH14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AI14">
         <v>5</v>
@@ -2329,7 +2278,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -2341,7 +2290,7 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -2353,31 +2302,31 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2410,7 +2359,7 @@
         <v>8</v>
       </c>
       <c r="AD15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE15">
         <v>9</v>
@@ -2419,19 +2368,19 @@
         <v>8</v>
       </c>
       <c r="AG15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AI15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ15">
         <v>-1</v>
       </c>
       <c r="AK15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2442,7 +2391,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -2454,7 +2403,7 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>6</v>
@@ -2466,31 +2415,31 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2523,7 +2472,7 @@
         <v>9</v>
       </c>
       <c r="AD16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE16">
         <v>7</v>
@@ -2532,19 +2481,19 @@
         <v>10</v>
       </c>
       <c r="AG16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AI16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ16">
         <v>-1</v>
       </c>
       <c r="AK16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2555,7 +2504,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -2567,7 +2516,7 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H17">
         <v>10</v>
@@ -2579,31 +2528,31 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2636,7 +2585,7 @@
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE17">
         <v>10</v>
@@ -2648,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="AH17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI17">
         <v>10</v>
@@ -2668,7 +2617,7 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -2680,7 +2629,7 @@
         <v>9</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>6</v>
@@ -2692,31 +2641,31 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2746,10 +2695,10 @@
         <v>-1</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE18">
         <v>10</v>
@@ -2758,13 +2707,13 @@
         <v>6</v>
       </c>
       <c r="AG18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AI18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ18">
         <v>-1</v>
@@ -2781,7 +2730,7 @@
         <v>9</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -2793,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H19">
         <v>9</v>
@@ -2805,31 +2754,31 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2859,10 +2808,10 @@
         <v>-1</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE19">
         <v>10</v>
@@ -2874,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="AH19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI19">
         <v>9</v>
@@ -2883,7 +2832,7 @@
         <v>-1</v>
       </c>
       <c r="AK19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2894,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -2906,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -2918,31 +2867,31 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2972,10 +2921,10 @@
         <v>-1</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE20">
         <v>9</v>
@@ -2987,16 +2936,16 @@
         <v>10</v>
       </c>
       <c r="AH20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AI20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ20">
         <v>-1</v>
       </c>
       <c r="AK20">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3007,7 +2956,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -3019,7 +2968,7 @@
         <v>9</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -3031,31 +2980,31 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -3088,7 +3037,7 @@
         <v>7</v>
       </c>
       <c r="AD21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE21">
         <v>9</v>
@@ -3097,13 +3046,13 @@
         <v>8</v>
       </c>
       <c r="AG21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ21">
         <v>-1</v>
@@ -3120,7 +3069,7 @@
         <v>4</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -3132,7 +3081,7 @@
         <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -3144,31 +3093,31 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -3198,10 +3147,10 @@
         <v>-1</v>
       </c>
       <c r="AC22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE22">
         <v>7</v>
@@ -3213,7 +3162,7 @@
         <v>9</v>
       </c>
       <c r="AH22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AI22">
         <v>5</v>
@@ -3233,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>9</v>
@@ -3245,7 +3194,7 @@
         <v>9</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -3257,31 +3206,31 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3314,7 +3263,7 @@
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE23">
         <v>9</v>
@@ -3323,19 +3272,19 @@
         <v>8</v>
       </c>
       <c r="AG23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ23">
         <v>-1</v>
       </c>
       <c r="AK23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3346,7 +3295,7 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -3358,7 +3307,7 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H24">
         <v>9</v>
@@ -3370,31 +3319,31 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3427,10 +3376,10 @@
         <v>10</v>
       </c>
       <c r="AD24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF24">
         <v>10</v>
@@ -3439,10 +3388,10 @@
         <v>10</v>
       </c>
       <c r="AH24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ24">
         <v>-1</v>
@@ -3459,7 +3408,7 @@
         <v>9</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -3471,7 +3420,7 @@
         <v>10</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -3483,31 +3432,31 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3537,13 +3486,13 @@
         <v>-1</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF25">
         <v>8</v>
@@ -3552,16 +3501,16 @@
         <v>10</v>
       </c>
       <c r="AH25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ25">
         <v>-1</v>
       </c>
       <c r="AK25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3569,10 +3518,10 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>9</v>
@@ -3584,7 +3533,7 @@
         <v>10</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>7</v>
@@ -3596,31 +3545,31 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3650,13 +3599,13 @@
         <v>-1</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF26">
         <v>10</v>
@@ -3665,7 +3614,7 @@
         <v>10</v>
       </c>
       <c r="AH26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AI26">
         <v>7</v>
@@ -3685,7 +3634,7 @@
         <v>9</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -3697,7 +3646,7 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H27">
         <v>6</v>
@@ -3709,31 +3658,31 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3763,10 +3712,10 @@
         <v>-1</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE27">
         <v>7</v>
@@ -3775,13 +3724,13 @@
         <v>9</v>
       </c>
       <c r="AG27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AI27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ27">
         <v>-1</v>
@@ -3798,7 +3747,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>10</v>
@@ -3810,7 +3759,7 @@
         <v>10</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -3822,31 +3771,31 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3879,7 +3828,7 @@
         <v>10</v>
       </c>
       <c r="AD28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE28">
         <v>10</v>
@@ -3891,16 +3840,16 @@
         <v>10</v>
       </c>
       <c r="AH28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ28">
         <v>-1</v>
       </c>
       <c r="AK28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3911,7 +3860,7 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -3923,7 +3872,7 @@
         <v>10</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -3935,31 +3884,31 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3989,10 +3938,10 @@
         <v>-1</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE29">
         <v>9</v>
@@ -4004,10 +3953,10 @@
         <v>10</v>
       </c>
       <c r="AH29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ29">
         <v>-1</v>
@@ -4024,7 +3973,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>9</v>
@@ -4036,7 +3985,7 @@
         <v>10</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H30">
         <v>6</v>
@@ -4048,31 +3997,31 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -4105,10 +4054,10 @@
         <v>8</v>
       </c>
       <c r="AD30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF30">
         <v>7</v>
@@ -4117,10 +4066,10 @@
         <v>10</v>
       </c>
       <c r="AH30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ30">
         <v>-1</v>
@@ -4137,7 +4086,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -4149,7 +4098,7 @@
         <v>6</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>6</v>
@@ -4161,31 +4110,31 @@
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -4215,13 +4164,13 @@
         <v>-1</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF31">
         <v>6</v>
@@ -4230,7 +4179,7 @@
         <v>6</v>
       </c>
       <c r="AH31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI31">
         <v>6</v>
@@ -4250,7 +4199,7 @@
         <v>4</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -4262,7 +4211,7 @@
         <v>7</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -4274,31 +4223,31 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -4331,7 +4280,7 @@
         <v>5</v>
       </c>
       <c r="AD32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE32">
         <v>6</v>
@@ -4340,10 +4289,10 @@
         <v>8</v>
       </c>
       <c r="AG32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AI32">
         <v>5</v>
@@ -4363,7 +4312,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>9</v>
@@ -4375,7 +4324,7 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H33">
         <v>6</v>
@@ -4387,31 +4336,31 @@
         <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -4441,10 +4390,10 @@
         <v>-1</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE33">
         <v>9</v>
@@ -4456,10 +4405,10 @@
         <v>10</v>
       </c>
       <c r="AH33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AI33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ33">
         <v>-1</v>
@@ -4476,7 +4425,7 @@
         <v>6</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>9</v>
@@ -4488,7 +4437,7 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H34">
         <v>6</v>
@@ -4500,31 +4449,31 @@
         <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>-1</v>
@@ -4554,22 +4503,22 @@
         <v>-1</v>
       </c>
       <c r="AC34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF34">
         <v>6</v>
       </c>
       <c r="AG34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI34">
         <v>6</v>
@@ -4578,7 +4527,7 @@
         <v>-1</v>
       </c>
       <c r="AK34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -4589,7 +4538,7 @@
         <v>4</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -4601,7 +4550,7 @@
         <v>10</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -4613,31 +4562,31 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
         <v>-1</v>
@@ -4667,10 +4616,10 @@
         <v>-1</v>
       </c>
       <c r="AC35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE35">
         <v>6</v>
@@ -4679,10 +4628,10 @@
         <v>6</v>
       </c>
       <c r="AG35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI35">
         <v>5</v>
@@ -4702,7 +4651,7 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -4714,7 +4663,7 @@
         <v>9</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>6</v>
@@ -4726,31 +4675,31 @@
         <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>-1</v>
@@ -4780,10 +4729,10 @@
         <v>-1</v>
       </c>
       <c r="AC36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE36">
         <v>7</v>
@@ -4792,19 +4741,19 @@
         <v>9</v>
       </c>
       <c r="AG36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ36">
         <v>-1</v>
       </c>
       <c r="AK36">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -4815,7 +4764,7 @@
         <v>8</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>9</v>
@@ -4827,7 +4776,7 @@
         <v>9</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H37">
         <v>6</v>
@@ -4839,31 +4788,31 @@
         <v>9</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>-1</v>
@@ -4896,7 +4845,7 @@
         <v>8</v>
       </c>
       <c r="AD37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE37">
         <v>9</v>
@@ -4905,19 +4854,19 @@
         <v>9</v>
       </c>
       <c r="AG37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ37">
         <v>-1</v>
       </c>
       <c r="AK37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:37">
@@ -4928,7 +4877,7 @@
         <v>4</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>7</v>
@@ -4940,7 +4889,7 @@
         <v>8</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>6</v>
@@ -4952,31 +4901,31 @@
         <v>4</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
         <v>-1</v>
@@ -5006,10 +4955,10 @@
         <v>-1</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE38">
         <v>7</v>
@@ -5018,13 +4967,13 @@
         <v>5</v>
       </c>
       <c r="AG38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AI38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ38">
         <v>-1</v>
@@ -5041,7 +4990,7 @@
         <v>10</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>9</v>
@@ -5053,7 +5002,7 @@
         <v>10</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -5065,31 +5014,31 @@
         <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
         <v>-1</v>
@@ -5122,7 +5071,7 @@
         <v>10</v>
       </c>
       <c r="AD39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE39">
         <v>9</v>
@@ -5134,16 +5083,16 @@
         <v>10</v>
       </c>
       <c r="AH39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ39">
         <v>-1</v>
       </c>
       <c r="AK39">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:37">
@@ -5154,7 +5103,7 @@
         <v>9</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D40">
         <v>9</v>
@@ -5166,7 +5115,7 @@
         <v>10</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H40">
         <v>7</v>
@@ -5178,31 +5127,31 @@
         <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
         <v>-1</v>
@@ -5232,13 +5181,13 @@
         <v>-1</v>
       </c>
       <c r="AC40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF40">
         <v>9</v>
@@ -5247,10 +5196,10 @@
         <v>10</v>
       </c>
       <c r="AH40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ40">
         <v>-1</v>
@@ -5267,7 +5216,7 @@
         <v>8</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -5279,7 +5228,7 @@
         <v>9</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H41">
         <v>6</v>
@@ -5291,31 +5240,31 @@
         <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
         <v>-1</v>
@@ -5348,28 +5297,28 @@
         <v>8</v>
       </c>
       <c r="AD41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF41">
         <v>5</v>
       </c>
       <c r="AG41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AI41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ41">
         <v>-1</v>
       </c>
       <c r="AK41">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5526,7 +5475,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -5538,7 +5487,7 @@
         <v>93.8</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -5550,10 +5499,10 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -5565,7 +5514,7 @@
         <v>93.8</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -5577,10 +5526,10 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -5592,7 +5541,7 @@
         <v>93.8</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z4">
         <v>100</v>
@@ -5612,7 +5561,7 @@
         <v>75</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -5624,7 +5573,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H5">
         <v>90</v>
@@ -5636,10 +5585,10 @@
         <v>90</v>
       </c>
       <c r="K5">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -5648,25 +5597,25 @@
         <v>93.3</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="T5">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -5675,19 +5624,19 @@
         <v>93.3</v>
       </c>
       <c r="X5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="Z5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="AA5">
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -5698,7 +5647,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -5710,7 +5659,7 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>100</v>
@@ -5722,10 +5671,10 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -5737,10 +5686,10 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -5749,10 +5698,10 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -5764,10 +5713,10 @@
         <v>100</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA6">
         <v>100</v>
@@ -5784,7 +5733,7 @@
         <v>91.7</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -5796,7 +5745,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -5808,10 +5757,10 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>91.7</v>
+        <v>81.8</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -5820,10 +5769,10 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -5835,10 +5784,10 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>91.7</v>
+        <v>81.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -5847,10 +5796,10 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z7">
         <v>100</v>
@@ -5870,7 +5819,7 @@
         <v>91.7</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -5882,7 +5831,7 @@
         <v>93.8</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -5894,10 +5843,10 @@
         <v>90</v>
       </c>
       <c r="K8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -5909,7 +5858,7 @@
         <v>93.8</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -5918,13 +5867,13 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -5936,7 +5885,7 @@
         <v>93.8</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z8">
         <v>100</v>
@@ -5945,7 +5894,7 @@
         <v>100</v>
       </c>
       <c r="AB8">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -5956,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -5968,7 +5917,7 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -5980,10 +5929,10 @@
         <v>96.7</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -5992,10 +5941,10 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -6004,13 +5953,13 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -6019,10 +5968,10 @@
         <v>100</v>
       </c>
       <c r="X9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="Z9">
         <v>100</v>
@@ -6031,7 +5980,7 @@
         <v>100</v>
       </c>
       <c r="AB9">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -6042,7 +5991,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -6054,7 +6003,7 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -6069,7 +6018,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -6081,22 +6030,22 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R10">
         <v>100</v>
       </c>
       <c r="S10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="T10">
         <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -6108,16 +6057,16 @@
         <v>100</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA10">
         <v>100</v>
       </c>
       <c r="AB10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -6128,7 +6077,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -6140,7 +6089,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -6152,10 +6101,10 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -6164,10 +6113,10 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -6179,10 +6128,10 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -6191,10 +6140,10 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z11">
         <v>100</v>
@@ -6214,7 +6163,7 @@
         <v>75</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -6226,7 +6175,7 @@
         <v>62.5</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -6238,10 +6187,10 @@
         <v>95</v>
       </c>
       <c r="K12">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -6250,25 +6199,25 @@
         <v>66.7</v>
       </c>
       <c r="O12">
-        <v>62.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R12">
         <v>100</v>
       </c>
       <c r="S12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T12">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -6277,19 +6226,19 @@
         <v>66.7</v>
       </c>
       <c r="X12">
-        <v>62.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Z12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA12">
         <v>100</v>
       </c>
       <c r="AB12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -6300,7 +6249,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -6312,7 +6261,7 @@
         <v>93.8</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>100</v>
@@ -6324,10 +6273,10 @@
         <v>96.7</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -6339,7 +6288,7 @@
         <v>93.8</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -6348,13 +6297,13 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -6366,7 +6315,7 @@
         <v>93.8</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z13">
         <v>100</v>
@@ -6375,7 +6324,7 @@
         <v>100</v>
       </c>
       <c r="AB13">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -6386,7 +6335,7 @@
         <v>75</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -6398,7 +6347,7 @@
         <v>62.5</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H14">
         <v>95</v>
@@ -6410,10 +6359,10 @@
         <v>90</v>
       </c>
       <c r="K14">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -6422,25 +6371,25 @@
         <v>66.7</v>
       </c>
       <c r="O14">
-        <v>62.5</v>
+        <v>46.9</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="Q14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="T14">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -6449,19 +6398,19 @@
         <v>66.7</v>
       </c>
       <c r="X14">
-        <v>62.5</v>
+        <v>46.9</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="Z14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA14">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB14">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -6472,7 +6421,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -6484,7 +6433,7 @@
         <v>93.8</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>100</v>
@@ -6496,10 +6445,10 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -6508,10 +6457,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -6523,10 +6472,10 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -6535,10 +6484,10 @@
         <v>100</v>
       </c>
       <c r="X15">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z15">
         <v>100</v>
@@ -6558,7 +6507,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -6570,7 +6519,7 @@
         <v>93.8</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -6582,10 +6531,10 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -6597,7 +6546,7 @@
         <v>93.8</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -6609,10 +6558,10 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -6624,7 +6573,7 @@
         <v>93.8</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z16">
         <v>100</v>
@@ -6644,7 +6593,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -6656,7 +6605,7 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>100</v>
@@ -6668,10 +6617,10 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -6683,7 +6632,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -6695,10 +6644,10 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -6710,7 +6659,7 @@
         <v>100</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z17">
         <v>100</v>
@@ -6730,7 +6679,7 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -6742,7 +6691,7 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -6754,10 +6703,10 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -6769,7 +6718,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -6781,10 +6730,10 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -6796,7 +6745,7 @@
         <v>100</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z18">
         <v>100</v>
@@ -6816,7 +6765,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -6828,7 +6777,7 @@
         <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>100</v>
@@ -6843,7 +6792,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -6855,7 +6804,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -6870,7 +6819,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -6882,7 +6831,7 @@
         <v>100</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z19">
         <v>100</v>
@@ -6902,7 +6851,7 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -6914,7 +6863,7 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20">
         <v>95</v>
@@ -6926,10 +6875,10 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -6941,22 +6890,22 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -6968,16 +6917,16 @@
         <v>100</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="AA20">
         <v>100</v>
       </c>
       <c r="AB20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="21" spans="1:28">
@@ -6988,7 +6937,7 @@
         <v>83.3</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -7000,7 +6949,7 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H21">
         <v>100</v>
@@ -7012,10 +6961,10 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -7027,7 +6976,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -7036,13 +6985,13 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T21">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -7054,7 +7003,7 @@
         <v>100</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Z21">
         <v>100</v>
@@ -7063,7 +7012,7 @@
         <v>100</v>
       </c>
       <c r="AB21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="22" spans="1:28">
@@ -7074,7 +7023,7 @@
         <v>66.7</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -7086,7 +7035,7 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>95</v>
@@ -7098,10 +7047,10 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -7110,13 +7059,13 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -7125,10 +7074,10 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -7137,13 +7086,13 @@
         <v>100</v>
       </c>
       <c r="X22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="AA22">
         <v>100</v>
@@ -7160,7 +7109,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -7172,7 +7121,7 @@
         <v>100</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23">
         <v>95</v>
@@ -7187,7 +7136,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -7196,13 +7145,13 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -7214,7 +7163,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -7223,13 +7172,13 @@
         <v>100</v>
       </c>
       <c r="X23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -7246,7 +7195,7 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -7258,7 +7207,7 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
         <v>100</v>
@@ -7270,10 +7219,10 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -7285,7 +7234,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -7297,10 +7246,10 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -7312,7 +7261,7 @@
         <v>100</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24">
         <v>100</v>
@@ -7332,7 +7281,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -7344,7 +7293,7 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H25">
         <v>100</v>
@@ -7356,10 +7305,10 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -7368,13 +7317,13 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -7383,10 +7332,10 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -7395,13 +7344,13 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Z25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA25">
         <v>100</v>
@@ -7418,7 +7367,7 @@
         <v>83.3</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -7430,7 +7379,7 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26">
         <v>100</v>
@@ -7442,10 +7391,10 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -7457,7 +7406,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -7469,10 +7418,10 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -7484,7 +7433,7 @@
         <v>100</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z26">
         <v>100</v>
@@ -7504,7 +7453,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -7516,7 +7465,7 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H27">
         <v>90</v>
@@ -7528,10 +7477,10 @@
         <v>95</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -7540,25 +7489,25 @@
         <v>86.7</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>95</v>
+        <v>94.2</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -7567,19 +7516,19 @@
         <v>86.7</v>
       </c>
       <c r="X27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA27">
         <v>100</v>
       </c>
       <c r="AB27">
-        <v>95</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="28" spans="1:28">
@@ -7590,7 +7539,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -7602,7 +7551,7 @@
         <v>100</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H28">
         <v>100</v>
@@ -7617,7 +7566,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -7626,10 +7575,10 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -7638,13 +7587,13 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="T28">
         <v>100</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -7653,10 +7602,10 @@
         <v>100</v>
       </c>
       <c r="X28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z28">
         <v>100</v>
@@ -7665,7 +7614,7 @@
         <v>100</v>
       </c>
       <c r="AB28">
-        <v>93.3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:28">
@@ -7676,7 +7625,7 @@
         <v>91.7</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -7688,7 +7637,7 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>100</v>
@@ -7700,10 +7649,10 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -7712,10 +7661,10 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -7727,10 +7676,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -7739,10 +7688,10 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z29">
         <v>100</v>
@@ -7762,7 +7711,7 @@
         <v>91.7</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -7774,7 +7723,7 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <v>100</v>
@@ -7786,10 +7735,10 @@
         <v>96.7</v>
       </c>
       <c r="K30">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -7801,7 +7750,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -7810,13 +7759,13 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="T30">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -7828,7 +7777,7 @@
         <v>100</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z30">
         <v>100</v>
@@ -7837,7 +7786,7 @@
         <v>100</v>
       </c>
       <c r="AB30">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="31" spans="1:28">
@@ -7848,7 +7797,7 @@
         <v>83.3</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -7860,7 +7809,7 @@
         <v>93.8</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>100</v>
@@ -7872,10 +7821,10 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -7887,7 +7836,7 @@
         <v>93.8</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -7899,10 +7848,10 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -7914,7 +7863,7 @@
         <v>93.8</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z31">
         <v>100</v>
@@ -7934,7 +7883,7 @@
         <v>66.7</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -7946,7 +7895,7 @@
         <v>87.5</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H32">
         <v>90</v>
@@ -7958,10 +7907,10 @@
         <v>93.3</v>
       </c>
       <c r="K32">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -7973,22 +7922,22 @@
         <v>87.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Q32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="T32">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -8000,16 +7949,16 @@
         <v>87.5</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Z32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA32">
         <v>100</v>
       </c>
       <c r="AB32">
-        <v>93.3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -8020,7 +7969,7 @@
         <v>91.7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -8032,7 +7981,7 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>100</v>
@@ -8044,10 +7993,10 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -8056,10 +8005,10 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -8071,10 +8020,10 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -8083,10 +8032,10 @@
         <v>100</v>
       </c>
       <c r="X33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z33">
         <v>100</v>
@@ -8106,7 +8055,7 @@
         <v>83.3</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -8118,7 +8067,7 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -8130,10 +8079,10 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -8142,25 +8091,25 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="T34">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -8169,19 +8118,19 @@
         <v>100</v>
       </c>
       <c r="X34">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z34">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="AA34">
         <v>100</v>
       </c>
       <c r="AB34">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="35" spans="1:28">
@@ -8192,7 +8141,7 @@
         <v>83.3</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -8204,7 +8153,7 @@
         <v>100</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35">
         <v>100</v>
@@ -8216,10 +8165,10 @@
         <v>96.7</v>
       </c>
       <c r="K35">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -8231,7 +8180,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -8240,13 +8189,13 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="T35">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -8258,7 +8207,7 @@
         <v>100</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z35">
         <v>100</v>
@@ -8267,7 +8216,7 @@
         <v>100</v>
       </c>
       <c r="AB35">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="36" spans="1:28">
@@ -8278,7 +8227,7 @@
         <v>91.7</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -8290,7 +8239,7 @@
         <v>87.5</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>95</v>
@@ -8302,10 +8251,10 @@
         <v>96.7</v>
       </c>
       <c r="K36">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -8314,10 +8263,10 @@
         <v>93.3</v>
       </c>
       <c r="O36">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
         <v>95</v>
@@ -8329,10 +8278,10 @@
         <v>96.7</v>
       </c>
       <c r="T36">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -8341,10 +8290,10 @@
         <v>93.3</v>
       </c>
       <c r="X36">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z36">
         <v>95</v>
@@ -8364,7 +8313,7 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -8376,7 +8325,7 @@
         <v>87.5</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>100</v>
@@ -8391,7 +8340,7 @@
         <v>100</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -8400,10 +8349,10 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -8418,7 +8367,7 @@
         <v>100</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V37">
         <v>100</v>
@@ -8427,10 +8376,10 @@
         <v>100</v>
       </c>
       <c r="X37">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z37">
         <v>100</v>
@@ -8450,7 +8399,7 @@
         <v>83.3</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -8462,7 +8411,7 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H38">
         <v>100</v>
@@ -8474,10 +8423,10 @@
         <v>96.7</v>
       </c>
       <c r="K38">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38">
         <v>100</v>
@@ -8486,10 +8435,10 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -8498,13 +8447,13 @@
         <v>100</v>
       </c>
       <c r="S38">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="T38">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V38">
         <v>100</v>
@@ -8513,10 +8462,10 @@
         <v>100</v>
       </c>
       <c r="X38">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z38">
         <v>100</v>
@@ -8525,7 +8474,7 @@
         <v>100</v>
       </c>
       <c r="AB38">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="39" spans="1:28">
@@ -8536,7 +8485,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>100</v>
@@ -8548,7 +8497,7 @@
         <v>100</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>95</v>
@@ -8563,7 +8512,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -8575,10 +8524,10 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q39">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -8590,7 +8539,7 @@
         <v>100</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -8602,10 +8551,10 @@
         <v>100</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z39">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="AA39">
         <v>100</v>
@@ -8622,7 +8571,7 @@
         <v>100</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>100</v>
@@ -8634,7 +8583,7 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>100</v>
@@ -8649,7 +8598,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40">
         <v>100</v>
@@ -8661,7 +8610,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -8676,7 +8625,7 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -8688,7 +8637,7 @@
         <v>100</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z40">
         <v>100</v>
@@ -8708,7 +8657,7 @@
         <v>100</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>100</v>
@@ -8720,7 +8669,7 @@
         <v>100</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41">
         <v>100</v>
@@ -8735,7 +8684,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41">
         <v>100</v>
@@ -8744,10 +8693,10 @@
         <v>93.3</v>
       </c>
       <c r="O41">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -8756,13 +8705,13 @@
         <v>100</v>
       </c>
       <c r="S41">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="T41">
         <v>100</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41">
         <v>100</v>
@@ -8771,10 +8720,10 @@
         <v>93.3</v>
       </c>
       <c r="X41">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z41">
         <v>100</v>
@@ -8783,7 +8732,7 @@
         <v>100</v>
       </c>
       <c r="AB41">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
   </sheetData>
@@ -8840,7 +8789,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -8869,7 +8818,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -8878,27 +8827,30 @@
         <v>38</v>
       </c>
       <c r="D3">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>76.3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3" s="2">
         <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>38</v>
-      </c>
-      <c r="J3" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -8907,27 +8859,30 @@
         <v>38</v>
       </c>
       <c r="D4">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <v>18.4</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="J4" s="2">
         <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>38</v>
-      </c>
-      <c r="J4" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -8936,19 +8891,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G5" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8968,19 +8923,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G6" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8991,7 +8946,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -9000,19 +8955,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>81.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="G7" s="2">
-        <v>18.4</v>
+        <v>10.5</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -9023,7 +8978,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -9032,19 +8987,19 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>84.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="H8">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9055,7 +9010,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
@@ -9064,19 +9019,19 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>86.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G9" s="2">
-        <v>13.2</v>
+        <v>7.9</v>
       </c>
       <c r="H9">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9087,7 +9042,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>73</v>
@@ -9096,19 +9051,19 @@
         <v>38</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G10" s="2">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="H10">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -9124,7 +9079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9151,1526 +9106,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920116</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920116</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330061460232</v>
-      </c>
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330061460232</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920117</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920117</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920118</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920118</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330061460223</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330061460223</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920119</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920119</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920120</v>
-      </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920120</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920121</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" t="s">
-        <v>145</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920121</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920424</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920424</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920224</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920224</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920124</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920124</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" t="s">
-        <v>148</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920125</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920125</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920126</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920126</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920127</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920127</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920128</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920128</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>23330051920129</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>23330051920129</v>
-      </c>
-      <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>23330051920130</v>
-      </c>
-      <c r="B34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>23330051920130</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>23330051920133</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>23330051920133</v>
-      </c>
-      <c r="B37" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" t="s">
-        <v>155</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>23330051920134</v>
-      </c>
-      <c r="B38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" t="s">
-        <v>156</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>23330051920134</v>
-      </c>
-      <c r="B39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" t="s">
-        <v>156</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>23330051920135</v>
-      </c>
-      <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>23330051920135</v>
-      </c>
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" t="s">
-        <v>157</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>23330051920137</v>
-      </c>
-      <c r="B42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" t="s">
-        <v>125</v>
-      </c>
-      <c r="D42" t="s">
-        <v>158</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>23330051920137</v>
-      </c>
-      <c r="B43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" t="s">
-        <v>125</v>
-      </c>
-      <c r="D43" t="s">
-        <v>158</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>23330051920122</v>
-      </c>
-      <c r="B44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>126</v>
-      </c>
-      <c r="D44" t="s">
-        <v>159</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>23330051920122</v>
-      </c>
-      <c r="B45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" t="s">
-        <v>126</v>
-      </c>
-      <c r="D45" t="s">
-        <v>159</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>23330051920140</v>
-      </c>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>119</v>
-      </c>
-      <c r="D46" t="s">
-        <v>160</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>23330051920140</v>
-      </c>
-      <c r="B47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" t="s">
-        <v>160</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>23330051920139</v>
-      </c>
-      <c r="B48" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" t="s">
-        <v>161</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>23330051920139</v>
-      </c>
-      <c r="B49" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" t="s">
-        <v>127</v>
-      </c>
-      <c r="D49" t="s">
-        <v>161</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>23330051920138</v>
-      </c>
-      <c r="B50" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" t="s">
-        <v>162</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>23330051920138</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" t="s">
-        <v>128</v>
-      </c>
-      <c r="D51" t="s">
-        <v>162</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>23330051920255</v>
-      </c>
-      <c r="B52" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" t="s">
-        <v>163</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>23330051920255</v>
-      </c>
-      <c r="B53" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" t="s">
-        <v>129</v>
-      </c>
-      <c r="D53" t="s">
-        <v>163</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>23330051920141</v>
-      </c>
-      <c r="B54" t="s">
-        <v>100</v>
-      </c>
-      <c r="C54" t="s">
-        <v>130</v>
-      </c>
-      <c r="D54" t="s">
-        <v>164</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>23330051920141</v>
-      </c>
-      <c r="B55" t="s">
-        <v>100</v>
-      </c>
-      <c r="C55" t="s">
-        <v>130</v>
-      </c>
-      <c r="D55" t="s">
-        <v>164</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>23330051920315</v>
-      </c>
-      <c r="B56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C56" t="s">
-        <v>131</v>
-      </c>
-      <c r="D56" t="s">
-        <v>165</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>23330051920315</v>
-      </c>
-      <c r="B57" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" t="s">
-        <v>131</v>
-      </c>
-      <c r="D57" t="s">
-        <v>165</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>23330051920142</v>
-      </c>
-      <c r="B58" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" t="s">
-        <v>132</v>
-      </c>
-      <c r="D58" t="s">
-        <v>166</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>23330051920142</v>
-      </c>
-      <c r="B59" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" t="s">
-        <v>132</v>
-      </c>
-      <c r="D59" t="s">
-        <v>166</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>23330051920143</v>
-      </c>
-      <c r="B60" t="s">
-        <v>103</v>
-      </c>
-      <c r="C60" t="s">
-        <v>133</v>
-      </c>
-      <c r="D60" t="s">
-        <v>167</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>23330051920143</v>
-      </c>
-      <c r="B61" t="s">
-        <v>103</v>
-      </c>
-      <c r="C61" t="s">
-        <v>133</v>
-      </c>
-      <c r="D61" t="s">
-        <v>167</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>23330051920144</v>
-      </c>
-      <c r="B62" t="s">
-        <v>104</v>
-      </c>
-      <c r="C62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" t="s">
-        <v>168</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>23330051920144</v>
-      </c>
-      <c r="B63" t="s">
-        <v>104</v>
-      </c>
-      <c r="C63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D63" t="s">
-        <v>168</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>23330051920145</v>
-      </c>
-      <c r="B64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C64" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" t="s">
-        <v>169</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>23330051920145</v>
-      </c>
-      <c r="B65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C65" t="s">
-        <v>106</v>
-      </c>
-      <c r="D65" t="s">
-        <v>169</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>23330051920146</v>
-      </c>
-      <c r="B66" t="s">
-        <v>106</v>
-      </c>
-      <c r="C66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66" t="s">
-        <v>170</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>23330051920146</v>
-      </c>
-      <c r="B67" t="s">
-        <v>106</v>
-      </c>
-      <c r="C67" t="s">
-        <v>89</v>
-      </c>
-      <c r="D67" t="s">
-        <v>170</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>23330051920147</v>
-      </c>
-      <c r="B68" t="s">
-        <v>107</v>
-      </c>
-      <c r="C68" t="s">
-        <v>134</v>
-      </c>
-      <c r="D68" t="s">
-        <v>171</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>23330051920147</v>
-      </c>
-      <c r="B69" t="s">
-        <v>107</v>
-      </c>
-      <c r="C69" t="s">
-        <v>134</v>
-      </c>
-      <c r="D69" t="s">
-        <v>171</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>23330051920346</v>
-      </c>
-      <c r="B70" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" t="s">
-        <v>135</v>
-      </c>
-      <c r="D70" t="s">
-        <v>172</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>23330051920346</v>
-      </c>
-      <c r="B71" t="s">
-        <v>108</v>
-      </c>
-      <c r="C71" t="s">
-        <v>135</v>
-      </c>
-      <c r="D71" t="s">
-        <v>172</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>23330051920148</v>
-      </c>
-      <c r="B72" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" t="s">
-        <v>89</v>
-      </c>
-      <c r="D72" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>23330051920148</v>
-      </c>
-      <c r="B73" t="s">
-        <v>109</v>
-      </c>
-      <c r="C73" t="s">
-        <v>89</v>
-      </c>
-      <c r="D73" t="s">
-        <v>173</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>23330051920149</v>
-      </c>
-      <c r="B74" t="s">
-        <v>110</v>
-      </c>
-      <c r="C74" t="s">
-        <v>136</v>
-      </c>
-      <c r="D74" t="s">
-        <v>174</v>
-      </c>
-      <c r="E74" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>23330051920149</v>
-      </c>
-      <c r="B75" t="s">
-        <v>110</v>
-      </c>
-      <c r="C75" t="s">
-        <v>136</v>
-      </c>
-      <c r="D75" t="s">
-        <v>174</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>23330051920150</v>
-      </c>
-      <c r="B76" t="s">
-        <v>111</v>
-      </c>
-      <c r="C76" t="s">
-        <v>137</v>
-      </c>
-      <c r="D76" t="s">
-        <v>175</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>23330051920150</v>
-      </c>
-      <c r="B77" t="s">
-        <v>111</v>
-      </c>
-      <c r="C77" t="s">
-        <v>137</v>
-      </c>
-      <c r="D77" t="s">
-        <v>175</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>66</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10678,7 +9113,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -10708,6 +9143,857 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920122</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920139</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920141</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920145</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920145</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920150</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920117</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330061460223</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920119</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920120</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920121</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920124</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920125</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920126</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920135</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920140</v>
+      </c>
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920138</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>23330051920255</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>23330051920315</v>
+      </c>
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>23330051920143</v>
+      </c>
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23330051920144</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" t="s">
+        <v>154</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>65</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>23330051920146</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>65</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>23330051920147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>23330051920346</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>23330051920149</v>
+      </c>
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>65</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2BLCM - Estadisticos 20232.xlsx
+++ b/grupos/2BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="162">
   <si>
     <t>Materia</t>
   </si>
@@ -221,24 +221,24 @@
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
@@ -254,247 +254,256 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BORBONIO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TENORIO</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BORBONIO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
+    <t>VOTE</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
+    <t>VIDAL</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>MANZANO</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SALINAS</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>VIDAL</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SALINAS</t>
+    <t>CAMILO</t>
   </si>
   <si>
     <t>DANIA LIZETH</t>
   </si>
   <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
+    <t>IRMA GUADALUPE</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>HELI AIMEE</t>
+  </si>
+  <si>
+    <t>AYLIN AMADA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CARLOS OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>SINAI</t>
+  </si>
+  <si>
+    <t>ARANTZA NAHOMI</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
+  </si>
+  <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MIRIAM NEFTALI</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>LEYLA SARAI</t>
+  </si>
+  <si>
+    <t>LUZ MARIA</t>
+  </si>
+  <si>
+    <t>NOELIA</t>
+  </si>
+  <si>
+    <t>VERONICA</t>
   </si>
   <si>
     <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>IRMA GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>AYLIN AMADA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CARLOS OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGELICA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>SINAI</t>
-  </si>
-  <si>
-    <t>ARANTZA NAHOMI</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MIRIAM NEFTALI</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
-  </si>
-  <si>
-    <t>NOELIA</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1077,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -1122,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="AF4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG4">
         <v>8</v>
@@ -1181,7 +1190,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1235,7 +1244,7 @@
         <v>5</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG5">
         <v>5</v>
@@ -1294,7 +1303,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1407,7 +1416,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>7</v>
@@ -1461,7 +1470,7 @@
         <v>7</v>
       </c>
       <c r="AF7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG7">
         <v>8</v>
@@ -1520,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1633,7 +1642,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1746,7 +1755,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1800,7 +1809,7 @@
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1859,7 +1868,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1972,7 +1981,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>8</v>
@@ -2085,7 +2094,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -2139,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="AF13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -2198,7 +2207,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -2311,7 +2320,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -2424,7 +2433,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>9</v>
@@ -2537,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2650,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -2704,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2763,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -2817,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="AF19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2876,7 +2885,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>9</v>
@@ -2930,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="AF20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2989,7 +2998,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -3043,7 +3052,7 @@
         <v>9</v>
       </c>
       <c r="AF21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -3102,7 +3111,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>9</v>
@@ -3156,7 +3165,7 @@
         <v>7</v>
       </c>
       <c r="AF22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG22">
         <v>9</v>
@@ -3215,7 +3224,7 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -3269,7 +3278,7 @@
         <v>9</v>
       </c>
       <c r="AF23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -3328,7 +3337,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -3441,7 +3450,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -3554,7 +3563,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -3667,7 +3676,7 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>9</v>
@@ -3721,7 +3730,7 @@
         <v>7</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>9</v>
@@ -3780,7 +3789,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -3893,7 +3902,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -3947,7 +3956,7 @@
         <v>9</v>
       </c>
       <c r="AF29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -4006,7 +4015,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>10</v>
@@ -4119,7 +4128,7 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -4173,7 +4182,7 @@
         <v>7</v>
       </c>
       <c r="AF31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG31">
         <v>6</v>
@@ -4232,7 +4241,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>5</v>
@@ -4345,7 +4354,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -4399,7 +4408,7 @@
         <v>9</v>
       </c>
       <c r="AF33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -4458,7 +4467,7 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>8</v>
@@ -4512,7 +4521,7 @@
         <v>8</v>
       </c>
       <c r="AF34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG34">
         <v>7</v>
@@ -4571,7 +4580,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>8</v>
@@ -4625,7 +4634,7 @@
         <v>6</v>
       </c>
       <c r="AF35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG35">
         <v>9</v>
@@ -4684,7 +4693,7 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
         <v>10</v>
@@ -4797,7 +4806,7 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
         <v>10</v>
@@ -4910,7 +4919,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>5</v>
@@ -4964,7 +4973,7 @@
         <v>7</v>
       </c>
       <c r="AF38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG38">
         <v>7</v>
@@ -5023,7 +5032,7 @@
         <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>10</v>
@@ -5136,7 +5145,7 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -5190,7 +5199,7 @@
         <v>10</v>
       </c>
       <c r="AF40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -5249,7 +5258,7 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>10</v>
@@ -5303,7 +5312,7 @@
         <v>9</v>
       </c>
       <c r="AF41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG41">
         <v>10</v>
@@ -5594,7 +5603,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="O5">
         <v>93.8</v>
@@ -5621,7 +5630,7 @@
         <v>100</v>
       </c>
       <c r="W5">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="X5">
         <v>93.8</v>
@@ -5852,7 +5861,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O8">
         <v>93.8</v>
@@ -5879,7 +5888,7 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X8">
         <v>93.8</v>
@@ -5938,7 +5947,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O9">
         <v>96.90000000000001</v>
@@ -5965,7 +5974,7 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X9">
         <v>96.90000000000001</v>
@@ -6024,7 +6033,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -6051,7 +6060,7 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="X10">
         <v>100</v>
@@ -6368,7 +6377,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="O14">
         <v>46.9</v>
@@ -6395,7 +6404,7 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="X14">
         <v>46.9</v>
@@ -7314,7 +7323,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="O25">
         <v>96.90000000000001</v>
@@ -7341,7 +7350,7 @@
         <v>100</v>
       </c>
       <c r="W25">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="X25">
         <v>96.90000000000001</v>
@@ -7400,7 +7409,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -7427,7 +7436,7 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -7744,7 +7753,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -7771,7 +7780,7 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -7830,7 +7839,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O31">
         <v>93.8</v>
@@ -7857,7 +7866,7 @@
         <v>100</v>
       </c>
       <c r="W31">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X31">
         <v>93.8</v>
@@ -7916,7 +7925,7 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O32">
         <v>87.5</v>
@@ -7943,7 +7952,7 @@
         <v>100</v>
       </c>
       <c r="W32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="X32">
         <v>87.5</v>
@@ -8260,7 +8269,7 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="O36">
         <v>90.59999999999999</v>
@@ -8287,7 +8296,7 @@
         <v>100</v>
       </c>
       <c r="W36">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="X36">
         <v>90.59999999999999</v>
@@ -8432,7 +8441,7 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O38">
         <v>93.8</v>
@@ -8459,7 +8468,7 @@
         <v>100</v>
       </c>
       <c r="W38">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X38">
         <v>93.8</v>
@@ -8518,7 +8527,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O39">
         <v>100</v>
@@ -8545,7 +8554,7 @@
         <v>100</v>
       </c>
       <c r="W39">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="X39">
         <v>100</v>
@@ -8604,7 +8613,7 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O40">
         <v>100</v>
@@ -8631,7 +8640,7 @@
         <v>100</v>
       </c>
       <c r="W40">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="X40">
         <v>100</v>
@@ -8850,7 +8859,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -8859,19 +8868,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>81.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="G4" s="2">
-        <v>18.4</v>
+        <v>15.8</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8882,7 +8891,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -8903,7 +8912,7 @@
         <v>15.8</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8914,7 +8923,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -8923,19 +8932,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>84.2</v>
+        <v>89.5</v>
       </c>
       <c r="G6" s="2">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8946,7 +8955,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -8955,19 +8964,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>89.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8978,7 +8987,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -8999,7 +9008,7 @@
         <v>7.9</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9010,7 +9019,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
@@ -9019,19 +9028,19 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="G9" s="2">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="H9">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9145,16 +9154,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920133</v>
+        <v>22330061460232</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -9168,16 +9177,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920133</v>
+        <v>22330061460232</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -9191,22 +9200,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920122</v>
+        <v>23330051920133</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -9214,16 +9223,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920122</v>
+        <v>23330051920133</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -9243,10 +9252,10 @@
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -9266,16 +9275,16 @@
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -9289,10 +9298,10 @@
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -9312,16 +9321,16 @@
         <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -9338,7 +9347,7 @@
         <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -9361,7 +9370,7 @@
         <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -9375,39 +9384,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920150</v>
+        <v>23330051920117</v>
       </c>
       <c r="B12" t="s">
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920150</v>
+        <v>23330061460223</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -9421,16 +9430,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920117</v>
+        <v>23330051920119</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -9444,16 +9453,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330061460223</v>
+        <v>23330051920120</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -9467,16 +9476,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920119</v>
+        <v>23330051920121</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -9490,16 +9499,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920120</v>
+        <v>23330051920124</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -9513,16 +9522,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920121</v>
+        <v>23330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -9536,16 +9545,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920124</v>
+        <v>23330051920126</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -9559,16 +9568,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920125</v>
+        <v>23330051920127</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -9582,16 +9591,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920126</v>
+        <v>23330051920128</v>
       </c>
       <c r="B21" t="s">
         <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -9605,16 +9614,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920127</v>
+        <v>23330051920129</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -9628,16 +9637,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920128</v>
+        <v>23330051920130</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -9651,16 +9660,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920129</v>
+        <v>23330051920134</v>
       </c>
       <c r="B24" t="s">
         <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -9674,16 +9683,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920130</v>
+        <v>23330051920135</v>
       </c>
       <c r="B25" t="s">
         <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -9697,16 +9706,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920134</v>
+        <v>23330051920137</v>
       </c>
       <c r="B26" t="s">
         <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -9720,16 +9729,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920135</v>
+        <v>23330051920122</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -9743,16 +9752,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920137</v>
+        <v>23330051920140</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -9766,16 +9775,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920140</v>
+        <v>23330051920138</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
@@ -9789,16 +9798,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920138</v>
+        <v>23330051920255</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
@@ -9812,16 +9821,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920255</v>
+        <v>23330051920315</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
@@ -9835,16 +9844,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920315</v>
+        <v>23330051920143</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E32" t="s">
         <v>12</v>
@@ -9858,16 +9867,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920143</v>
+        <v>23330051920144</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
@@ -9881,16 +9890,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920144</v>
+        <v>23330051920146</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
@@ -9904,16 +9913,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920146</v>
+        <v>23330051920147</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
@@ -9927,16 +9936,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920147</v>
+        <v>23330051920346</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
         <v>12</v>
@@ -9950,16 +9959,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920346</v>
+        <v>23330051920149</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E37" t="s">
         <v>12</v>
@@ -9973,16 +9982,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920149</v>
+        <v>23330051920150</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E38" t="s">
         <v>12</v>

--- a/grupos/2BLCM - Estadisticos 20232.xlsx
+++ b/grupos/2BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -221,27 +221,27 @@
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -254,75 +254,81 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>AMARO</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BORBONIO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>RUGERIO</t>
   </si>
   <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BORBONIO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -338,60 +344,60 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>VOTE</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ORTIZ</t>
   </si>
   <si>
+    <t>VIDAL</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VIDAL</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
     <t>MANZANO</t>
   </si>
   <si>
@@ -410,85 +416,91 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CAMILO</t>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>ABRIL AMAYRANI</t>
+  </si>
+  <si>
+    <t>IRMA GUADALUPE</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>HELI AIMEE</t>
+  </si>
+  <si>
+    <t>AYLIN AMADA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CARLOS OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>SINAI</t>
+  </si>
+  <si>
+    <t>ARANTZA NAHOMI</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
   </si>
   <si>
     <t>DANIA LIZETH</t>
   </si>
   <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MARITZA</t>
   </si>
   <si>
+    <t>MIRIAM NEFTALI</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
     <t>MARYGELLI</t>
   </si>
   <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
     <t>MAGALY</t>
-  </si>
-  <si>
-    <t>IRMA GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>AYLIN AMADA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CARLOS OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGELICA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>SINAI</t>
-  </si>
-  <si>
-    <t>ARANTZA NAHOMI</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MIRIAM NEFTALI</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
   </si>
   <si>
     <t>LEYLA SARAI</t>
@@ -1095,34 +1107,34 @@
         <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD4">
         <v>6</v>
@@ -1208,31 +1220,31 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1241,25 +1253,25 @@
         <v>6</v>
       </c>
       <c r="AE5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF5">
         <v>7</v>
       </c>
       <c r="AG5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ5">
         <v>-1</v>
       </c>
       <c r="AK5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1321,31 +1333,31 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>10</v>
@@ -1434,37 +1446,37 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>6</v>
       </c>
       <c r="AD7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE7">
         <v>7</v>
@@ -1476,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="AH7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI7">
         <v>5</v>
@@ -1485,7 +1497,7 @@
         <v>-1</v>
       </c>
       <c r="AK7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1547,46 +1559,46 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC8">
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE8">
         <v>7</v>
       </c>
       <c r="AF8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8">
         <v>8</v>
@@ -1660,31 +1672,31 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1773,31 +1785,31 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1815,7 +1827,7 @@
         <v>10</v>
       </c>
       <c r="AH10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10">
         <v>10</v>
@@ -1824,7 +1836,7 @@
         <v>-1</v>
       </c>
       <c r="AK10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1886,31 +1898,31 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1931,7 +1943,7 @@
         <v>10</v>
       </c>
       <c r="AI11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ11">
         <v>-1</v>
@@ -1999,49 +2011,49 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>5</v>
       </c>
       <c r="AD12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12">
         <v>5</v>
       </c>
       <c r="AG12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI12">
         <v>5</v>
@@ -2112,31 +2124,31 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -2154,16 +2166,16 @@
         <v>10</v>
       </c>
       <c r="AH13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ13">
         <v>-1</v>
       </c>
       <c r="AK13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2225,40 +2237,40 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD14">
         <v>5</v>
       </c>
       <c r="AE14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14">
         <v>5</v>
@@ -2338,31 +2350,31 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -2374,7 +2386,7 @@
         <v>9</v>
       </c>
       <c r="AF15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2451,37 +2463,37 @@
         <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE16">
         <v>7</v>
@@ -2490,7 +2502,7 @@
         <v>10</v>
       </c>
       <c r="AG16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH16">
         <v>9</v>
@@ -2564,31 +2576,31 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2677,31 +2689,31 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2719,7 +2731,7 @@
         <v>10</v>
       </c>
       <c r="AH18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI18">
         <v>7</v>
@@ -2790,31 +2802,31 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -2832,7 +2844,7 @@
         <v>10</v>
       </c>
       <c r="AH19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI19">
         <v>9</v>
@@ -2903,31 +2915,31 @@
         <v>4</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -2942,19 +2954,19 @@
         <v>8</v>
       </c>
       <c r="AG20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ20">
         <v>-1</v>
       </c>
       <c r="AK20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3016,31 +3028,31 @@
         <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -3055,19 +3067,19 @@
         <v>9</v>
       </c>
       <c r="AG21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ21">
         <v>-1</v>
       </c>
       <c r="AK21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3129,34 +3141,34 @@
         <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD22">
         <v>7</v>
@@ -3171,16 +3183,16 @@
         <v>9</v>
       </c>
       <c r="AH22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ22">
         <v>-1</v>
       </c>
       <c r="AK22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3242,34 +3254,34 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD23">
         <v>8</v>
@@ -3281,10 +3293,10 @@
         <v>9</v>
       </c>
       <c r="AG23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI23">
         <v>8</v>
@@ -3355,31 +3367,31 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -3468,40 +3480,40 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25">
         <v>8</v>
@@ -3510,7 +3522,7 @@
         <v>10</v>
       </c>
       <c r="AH25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI25">
         <v>7</v>
@@ -3519,7 +3531,7 @@
         <v>-1</v>
       </c>
       <c r="AK25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3581,31 +3593,31 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -3694,31 +3706,31 @@
         <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3727,16 +3739,16 @@
         <v>10</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG27">
         <v>9</v>
       </c>
       <c r="AH27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI27">
         <v>7</v>
@@ -3745,7 +3757,7 @@
         <v>-1</v>
       </c>
       <c r="AK27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3807,31 +3819,31 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC28">
         <v>10</v>
@@ -3843,22 +3855,22 @@
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG28">
         <v>10</v>
       </c>
       <c r="AH28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ28">
         <v>-1</v>
       </c>
       <c r="AK28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3920,31 +3932,31 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3956,7 +3968,7 @@
         <v>9</v>
       </c>
       <c r="AF29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3965,13 +3977,13 @@
         <v>8</v>
       </c>
       <c r="AI29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ29">
         <v>-1</v>
       </c>
       <c r="AK29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -4033,43 +4045,43 @@
         <v>5</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>8</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -4078,13 +4090,13 @@
         <v>8</v>
       </c>
       <c r="AI30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ30">
         <v>-1</v>
       </c>
       <c r="AK30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4146,31 +4158,31 @@
         <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -4185,7 +4197,7 @@
         <v>7</v>
       </c>
       <c r="AG31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH31">
         <v>8</v>
@@ -4197,7 +4209,7 @@
         <v>-1</v>
       </c>
       <c r="AK31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4259,31 +4271,31 @@
         <v>4</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC32">
         <v>5</v>
@@ -4298,10 +4310,10 @@
         <v>8</v>
       </c>
       <c r="AG32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI32">
         <v>5</v>
@@ -4310,7 +4322,7 @@
         <v>-1</v>
       </c>
       <c r="AK32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4372,31 +4384,31 @@
         <v>6</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -4414,10 +4426,10 @@
         <v>10</v>
       </c>
       <c r="AH33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ33">
         <v>-1</v>
@@ -4485,31 +4497,31 @@
         <v>7</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC34">
         <v>8</v>
@@ -4527,10 +4539,10 @@
         <v>7</v>
       </c>
       <c r="AH34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ34">
         <v>-1</v>
@@ -4598,40 +4610,40 @@
         <v>6</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD35">
         <v>6</v>
       </c>
       <c r="AE35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF35">
         <v>8</v>
@@ -4643,7 +4655,7 @@
         <v>8</v>
       </c>
       <c r="AI35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ35">
         <v>-1</v>
@@ -4711,49 +4723,49 @@
         <v>9</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC36">
         <v>8</v>
       </c>
       <c r="AD36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE36">
         <v>7</v>
       </c>
       <c r="AF36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG36">
         <v>10</v>
       </c>
       <c r="AH36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI36">
         <v>7</v>
@@ -4824,31 +4836,31 @@
         <v>7</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>8</v>
@@ -4937,49 +4949,49 @@
         <v>6</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC38">
         <v>6</v>
       </c>
       <c r="AD38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE38">
         <v>7</v>
       </c>
       <c r="AF38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG38">
         <v>7</v>
       </c>
       <c r="AH38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI38">
         <v>5</v>
@@ -4988,7 +5000,7 @@
         <v>-1</v>
       </c>
       <c r="AK38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:37">
@@ -5050,40 +5062,40 @@
         <v>7</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF39">
         <v>9</v>
@@ -5095,7 +5107,7 @@
         <v>8</v>
       </c>
       <c r="AI39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ39">
         <v>-1</v>
@@ -5163,31 +5175,31 @@
         <v>9</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC40">
         <v>10</v>
@@ -5196,10 +5208,10 @@
         <v>10</v>
       </c>
       <c r="AE40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -5214,7 +5226,7 @@
         <v>-1</v>
       </c>
       <c r="AK40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:37">
@@ -5276,40 +5288,40 @@
         <v>8</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC41">
         <v>8</v>
       </c>
       <c r="AD41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF41">
         <v>7</v>
@@ -5318,10 +5330,10 @@
         <v>10</v>
       </c>
       <c r="AH41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ41">
         <v>-1</v>
@@ -5535,7 +5547,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -5547,13 +5559,13 @@
         <v>100</v>
       </c>
       <c r="X4">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y4">
         <v>100</v>
       </c>
       <c r="Z4">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -5621,7 +5633,7 @@
         <v>85</v>
       </c>
       <c r="T5">
-        <v>72.7</v>
+        <v>81.3</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -5630,22 +5642,22 @@
         <v>100</v>
       </c>
       <c r="W5">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X5">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y5">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="Z5">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="AA5">
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -5707,7 +5719,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -5725,13 +5737,13 @@
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA6">
         <v>100</v>
       </c>
       <c r="AB6">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -5793,7 +5805,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -5805,13 +5817,13 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="Y7">
         <v>100</v>
       </c>
       <c r="Z7">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="AA7">
         <v>100</v>
@@ -5879,7 +5891,7 @@
         <v>95</v>
       </c>
       <c r="T8">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -5888,13 +5900,13 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>96.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X8">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="Y8">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Z8">
         <v>100</v>
@@ -5903,7 +5915,7 @@
         <v>100</v>
       </c>
       <c r="AB8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -5965,7 +5977,7 @@
         <v>98.3</v>
       </c>
       <c r="T9">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -5974,22 +5986,22 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="X9">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y9">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Z9">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA9">
         <v>100</v>
       </c>
       <c r="AB9">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -6051,7 +6063,7 @@
         <v>98.3</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -6060,22 +6072,22 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Y10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Z10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA10">
         <v>100</v>
       </c>
       <c r="AB10">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -6137,7 +6149,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -6149,7 +6161,7 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -6223,31 +6235,31 @@
         <v>97.5</v>
       </c>
       <c r="T12">
-        <v>72.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U12">
-        <v>81</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="V12">
         <v>100</v>
       </c>
       <c r="W12">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="X12">
-        <v>71.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="Y12">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="Z12">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="AA12">
         <v>100</v>
       </c>
       <c r="AB12">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -6309,7 +6321,7 @@
         <v>98.3</v>
       </c>
       <c r="T13">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -6318,10 +6330,10 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="X13">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -6333,7 +6345,7 @@
         <v>100</v>
       </c>
       <c r="AB13">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -6371,7 +6383,7 @@
         <v>68.2</v>
       </c>
       <c r="L14">
-        <v>35.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -6395,31 +6407,31 @@
         <v>85</v>
       </c>
       <c r="T14">
-        <v>68.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U14">
-        <v>35.7</v>
+        <v>85.5</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="X14">
-        <v>46.9</v>
+        <v>31.3</v>
       </c>
       <c r="Y14">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="Z14">
-        <v>85</v>
+        <v>56.3</v>
       </c>
       <c r="AA14">
-        <v>85</v>
+        <v>70.8</v>
       </c>
       <c r="AB14">
-        <v>85</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -6481,7 +6493,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -6493,7 +6505,7 @@
         <v>100</v>
       </c>
       <c r="X15">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -6567,7 +6579,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -6579,7 +6591,7 @@
         <v>100</v>
       </c>
       <c r="X16">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -6653,7 +6665,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -6739,7 +6751,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6911,7 +6923,7 @@
         <v>98.3</v>
       </c>
       <c r="T20">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -6926,16 +6938,16 @@
         <v>100</v>
       </c>
       <c r="Y20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Z20">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="AA20">
         <v>100</v>
       </c>
       <c r="AB20">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:28">
@@ -6997,7 +7009,7 @@
         <v>96.7</v>
       </c>
       <c r="T21">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -7012,16 +7024,16 @@
         <v>100</v>
       </c>
       <c r="Y21">
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="Z21">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA21">
         <v>100</v>
       </c>
       <c r="AB21">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:28">
@@ -7083,7 +7095,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>77.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -7095,13 +7107,13 @@
         <v>100</v>
       </c>
       <c r="X22">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y22">
         <v>100</v>
       </c>
       <c r="Z22">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA22">
         <v>100</v>
@@ -7181,13 +7193,13 @@
         <v>100</v>
       </c>
       <c r="X23">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y23">
         <v>100</v>
       </c>
       <c r="Z23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -7255,7 +7267,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -7279,7 +7291,7 @@
         <v>100</v>
       </c>
       <c r="AB24">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:28">
@@ -7341,7 +7353,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -7350,22 +7362,22 @@
         <v>100</v>
       </c>
       <c r="W25">
-        <v>86.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X25">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y25">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="Z25">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="AA25">
         <v>100</v>
       </c>
       <c r="AB25">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:28">
@@ -7427,7 +7439,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -7436,7 +7448,7 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -7513,7 +7525,7 @@
         <v>94.2</v>
       </c>
       <c r="T27">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -7522,22 +7534,22 @@
         <v>100</v>
       </c>
       <c r="W27">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="X27">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y27">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z27">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="AA27">
         <v>100</v>
       </c>
       <c r="AB27">
-        <v>94.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="28" spans="1:28">
@@ -7608,22 +7620,22 @@
         <v>100</v>
       </c>
       <c r="W28">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="X28">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y28">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z28">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA28">
         <v>100</v>
       </c>
       <c r="AB28">
-        <v>95</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="29" spans="1:28">
@@ -7685,7 +7697,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -7697,7 +7709,7 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -7771,7 +7783,7 @@
         <v>98.3</v>
       </c>
       <c r="T30">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -7780,7 +7792,7 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -7795,7 +7807,7 @@
         <v>100</v>
       </c>
       <c r="AB30">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:28">
@@ -7857,7 +7869,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7866,7 +7878,7 @@
         <v>100</v>
       </c>
       <c r="W31">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="X31">
         <v>93.8</v>
@@ -7943,7 +7955,7 @@
         <v>95</v>
       </c>
       <c r="T32">
-        <v>72.7</v>
+        <v>81.3</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -7952,22 +7964,22 @@
         <v>100</v>
       </c>
       <c r="W32">
-        <v>80</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="X32">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y32">
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="Z32">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA32">
         <v>100</v>
       </c>
       <c r="AB32">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -8029,7 +8041,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -8038,10 +8050,10 @@
         <v>100</v>
       </c>
       <c r="W33">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X33">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y33">
         <v>100</v>
@@ -8115,7 +8127,7 @@
         <v>98.3</v>
       </c>
       <c r="T34">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -8127,19 +8139,19 @@
         <v>100</v>
       </c>
       <c r="X34">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="Y34">
+        <v>97.5</v>
+      </c>
+      <c r="Z34">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="AA34">
+        <v>100</v>
+      </c>
+      <c r="AB34">
         <v>96.90000000000001</v>
-      </c>
-      <c r="Y34">
-        <v>100</v>
-      </c>
-      <c r="Z34">
-        <v>92.5</v>
-      </c>
-      <c r="AA34">
-        <v>100</v>
-      </c>
-      <c r="AB34">
-        <v>98.3</v>
       </c>
     </row>
     <row r="35" spans="1:28">
@@ -8201,7 +8213,7 @@
         <v>98.3</v>
       </c>
       <c r="T35">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -8219,13 +8231,13 @@
         <v>100</v>
       </c>
       <c r="Z35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA35">
         <v>100</v>
       </c>
       <c r="AB35">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:28">
@@ -8287,7 +8299,7 @@
         <v>96.7</v>
       </c>
       <c r="T36">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -8296,22 +8308,22 @@
         <v>100</v>
       </c>
       <c r="W36">
-        <v>80</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="X36">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y36">
         <v>100</v>
       </c>
       <c r="Z36">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="AA36">
         <v>100</v>
       </c>
       <c r="AB36">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:28">
@@ -8373,7 +8385,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -8385,7 +8397,7 @@
         <v>100</v>
       </c>
       <c r="X37">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y37">
         <v>100</v>
@@ -8459,7 +8471,7 @@
         <v>98.3</v>
       </c>
       <c r="T38">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -8468,13 +8480,13 @@
         <v>100</v>
       </c>
       <c r="W38">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X38">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y38">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Z38">
         <v>100</v>
@@ -8483,7 +8495,7 @@
         <v>100</v>
       </c>
       <c r="AB38">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:28">
@@ -8545,7 +8557,7 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U39">
         <v>100</v>
@@ -8554,7 +8566,7 @@
         <v>100</v>
       </c>
       <c r="W39">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X39">
         <v>100</v>
@@ -8563,7 +8575,7 @@
         <v>100</v>
       </c>
       <c r="Z39">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA39">
         <v>100</v>
@@ -8640,7 +8652,7 @@
         <v>100</v>
       </c>
       <c r="W40">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X40">
         <v>100</v>
@@ -8726,10 +8738,10 @@
         <v>100</v>
       </c>
       <c r="W41">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="X41">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="Y41">
         <v>100</v>
@@ -8741,7 +8753,7 @@
         <v>100</v>
       </c>
       <c r="AB41">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -8836,19 +8848,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>76.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>23.7</v>
+        <v>18.4</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8859,7 +8871,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -8868,19 +8880,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>84.2</v>
+        <v>86.8</v>
       </c>
       <c r="G4" s="2">
-        <v>15.8</v>
+        <v>13.2</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8891,7 +8903,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -8900,19 +8912,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="G5" s="2">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8923,7 +8935,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -8932,19 +8944,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G6" s="2">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8955,7 +8967,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -8964,19 +8976,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8987,7 +8999,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -8996,19 +9008,19 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>92.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9019,7 +9031,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
@@ -9028,19 +9040,19 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>94.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="H9">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9051,7 +9063,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>73</v>
@@ -9060,19 +9072,19 @@
         <v>38</v>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -9122,7 +9134,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9154,22 +9166,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330061460232</v>
+        <v>23330051920116</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -9177,16 +9189,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330061460232</v>
+        <v>23330051920116</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -9200,16 +9212,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920133</v>
+        <v>23330051920118</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -9223,16 +9235,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920133</v>
+        <v>23330051920118</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -9246,131 +9258,131 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920139</v>
+        <v>23330051920144</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920139</v>
+        <v>23330051920144</v>
       </c>
       <c r="B7" t="s">
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920141</v>
+        <v>23330051920148</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920141</v>
+        <v>23330051920148</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920145</v>
+        <v>23330051920117</v>
       </c>
       <c r="B10" t="s">
         <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920145</v>
+        <v>23330061460223</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -9384,16 +9396,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920117</v>
+        <v>23330051920119</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -9407,16 +9419,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330061460223</v>
+        <v>23330051920120</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -9430,16 +9442,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920119</v>
+        <v>23330051920121</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
         <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -9453,16 +9465,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920120</v>
+        <v>23330051920124</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -9476,16 +9488,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920121</v>
+        <v>23330051920125</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -9499,16 +9511,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920124</v>
+        <v>23330051920126</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -9522,16 +9534,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920125</v>
+        <v>23330051920127</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
         <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -9545,16 +9557,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920126</v>
+        <v>23330051920128</v>
       </c>
       <c r="B19" t="s">
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -9568,16 +9580,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920127</v>
+        <v>23330051920129</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
         <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -9591,16 +9603,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920128</v>
+        <v>23330051920130</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -9614,16 +9626,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920129</v>
+        <v>23330051920133</v>
       </c>
       <c r="B22" t="s">
         <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -9637,16 +9649,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920130</v>
+        <v>23330051920134</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -9660,16 +9672,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920134</v>
+        <v>23330051920135</v>
       </c>
       <c r="B24" t="s">
         <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -9683,16 +9695,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920135</v>
+        <v>23330051920137</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -9706,16 +9718,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920137</v>
+        <v>23330051920122</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -9729,16 +9741,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920122</v>
+        <v>23330051920140</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -9752,16 +9764,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920140</v>
+        <v>23330051920139</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -9778,13 +9790,13 @@
         <v>23330051920138</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
@@ -9801,13 +9813,13 @@
         <v>23330051920255</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
@@ -9821,16 +9833,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920315</v>
+        <v>23330051920141</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
@@ -9844,16 +9856,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920143</v>
+        <v>23330051920315</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E32" t="s">
         <v>12</v>
@@ -9867,16 +9879,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920144</v>
+        <v>23330051920143</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
@@ -9890,16 +9902,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920146</v>
+        <v>23330051920145</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
@@ -9913,16 +9925,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920147</v>
+        <v>23330051920146</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
@@ -9936,16 +9948,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920346</v>
+        <v>23330051920147</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E36" t="s">
         <v>12</v>
@@ -9959,16 +9971,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920149</v>
+        <v>23330051920346</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E37" t="s">
         <v>12</v>
@@ -9982,16 +9994,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920150</v>
+        <v>23330051920149</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E38" t="s">
         <v>12</v>
@@ -10000,6 +10012,29 @@
         <v>65</v>
       </c>
       <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>23330051920150</v>
+      </c>
+      <c r="B39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20232.xlsx
+++ b/grupos/2BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -215,27 +215,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
@@ -254,6 +254,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>AMARO</t>
   </si>
   <si>
@@ -266,154 +272,22 @@
     <t>TAPIA</t>
   </si>
   <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BORBONIO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>VOTE</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>VIDAL</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SALINAS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>CAMILO</t>
+  </si>
+  <si>
+    <t>KAREN AMERICA</t>
   </si>
   <si>
     <t>ISAAC</t>
@@ -426,96 +300,6 @@
   </si>
   <si>
     <t>ABRIL AMAYRANI</t>
-  </si>
-  <si>
-    <t>IRMA GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>AYLIN AMADA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CARLOS OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGELICA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>SINAI</t>
-  </si>
-  <si>
-    <t>ARANTZA NAHOMI</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>MIRIAM NEFTALI</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
-  </si>
-  <si>
-    <t>NOELIA</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +939,7 @@
         <v>5</v>
       </c>
       <c r="AJ4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK4">
         <v>6</v>
@@ -1268,7 +1052,7 @@
         <v>6</v>
       </c>
       <c r="AJ5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK5">
         <v>6</v>
@@ -1381,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="AJ6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK6">
         <v>10</v>
@@ -1494,7 +1278,7 @@
         <v>5</v>
       </c>
       <c r="AJ7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK7">
         <v>8</v>
@@ -1607,7 +1391,7 @@
         <v>9</v>
       </c>
       <c r="AJ8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -1720,7 +1504,7 @@
         <v>8</v>
       </c>
       <c r="AJ9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK9">
         <v>9</v>
@@ -1833,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="AJ10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK10">
         <v>9</v>
@@ -1946,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="AJ11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK11">
         <v>9</v>
@@ -2059,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="AJ12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK12">
         <v>7</v>
@@ -2172,7 +1956,7 @@
         <v>6</v>
       </c>
       <c r="AJ13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK13">
         <v>8</v>
@@ -2285,7 +2069,7 @@
         <v>5</v>
       </c>
       <c r="AJ14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK14">
         <v>5</v>
@@ -2398,7 +2182,7 @@
         <v>7</v>
       </c>
       <c r="AJ15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK15">
         <v>9</v>
@@ -2511,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="AJ16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK16">
         <v>9</v>
@@ -2624,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="AJ17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK17">
         <v>10</v>
@@ -2737,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="AJ18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK18">
         <v>9</v>
@@ -2850,7 +2634,7 @@
         <v>9</v>
       </c>
       <c r="AJ19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK19">
         <v>8</v>
@@ -2963,7 +2747,7 @@
         <v>6</v>
       </c>
       <c r="AJ20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK20">
         <v>8</v>
@@ -3076,7 +2860,7 @@
         <v>6</v>
       </c>
       <c r="AJ21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK21">
         <v>7</v>
@@ -3189,7 +2973,7 @@
         <v>6</v>
       </c>
       <c r="AJ22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK22">
         <v>8</v>
@@ -3302,7 +3086,7 @@
         <v>8</v>
       </c>
       <c r="AJ23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK23">
         <v>9</v>
@@ -3415,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="AJ24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK24">
         <v>10</v>
@@ -3528,7 +3312,7 @@
         <v>7</v>
       </c>
       <c r="AJ25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK25">
         <v>8</v>
@@ -3641,7 +3425,7 @@
         <v>7</v>
       </c>
       <c r="AJ26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK26">
         <v>9</v>
@@ -3754,7 +3538,7 @@
         <v>7</v>
       </c>
       <c r="AJ27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK27">
         <v>6</v>
@@ -3867,7 +3651,7 @@
         <v>7</v>
       </c>
       <c r="AJ28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK28">
         <v>7</v>
@@ -3980,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="AJ29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK29">
         <v>7</v>
@@ -4093,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="AJ30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK30">
         <v>6</v>
@@ -4206,7 +3990,7 @@
         <v>6</v>
       </c>
       <c r="AJ31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK31">
         <v>8</v>
@@ -4319,7 +4103,7 @@
         <v>5</v>
       </c>
       <c r="AJ32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK32">
         <v>6</v>
@@ -4432,7 +4216,7 @@
         <v>6</v>
       </c>
       <c r="AJ33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK33">
         <v>7</v>
@@ -4545,7 +4329,7 @@
         <v>5</v>
       </c>
       <c r="AJ34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK34">
         <v>6</v>
@@ -4658,7 +4442,7 @@
         <v>6</v>
       </c>
       <c r="AJ35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK35">
         <v>7</v>
@@ -4771,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="AJ36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK36">
         <v>8</v>
@@ -4884,7 +4668,7 @@
         <v>7</v>
       </c>
       <c r="AJ37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK37">
         <v>8</v>
@@ -4997,7 +4781,7 @@
         <v>5</v>
       </c>
       <c r="AJ38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK38">
         <v>6</v>
@@ -5110,7 +4894,7 @@
         <v>6</v>
       </c>
       <c r="AJ39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK39">
         <v>9</v>
@@ -5223,7 +5007,7 @@
         <v>8</v>
       </c>
       <c r="AJ40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK40">
         <v>9</v>
@@ -5336,7 +5120,7 @@
         <v>6</v>
       </c>
       <c r="AJ41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK41">
         <v>7</v>
@@ -8810,7 +8594,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -8819,27 +8603,30 @@
         <v>38</v>
       </c>
       <c r="D2">
+        <v>31</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="G2" s="2">
+        <v>18.4</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>38</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -8848,19 +8635,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>81.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="G3" s="2">
-        <v>18.4</v>
+        <v>13.2</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8871,7 +8658,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -8880,19 +8667,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>86.8</v>
+        <v>94.7</v>
       </c>
       <c r="G4" s="2">
-        <v>13.2</v>
+        <v>5.3</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8903,7 +8690,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -8924,7 +8711,7 @@
         <v>5.3</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8935,7 +8722,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -8944,19 +8731,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>94.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8967,7 +8754,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -8988,7 +8775,7 @@
         <v>2.6</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8999,7 +8786,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -9020,7 +8807,7 @@
         <v>2.6</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9134,7 +8921,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9166,22 +8953,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920116</v>
+        <v>22330061460232</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -9189,42 +8976,42 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920116</v>
+        <v>22330061460232</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920118</v>
+        <v>23330051920142</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -9235,42 +9022,42 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920118</v>
+        <v>23330051920142</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920144</v>
+        <v>23330051920116</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
@@ -9281,45 +9068,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920144</v>
+        <v>23330051920118</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920148</v>
+        <v>23330051920144</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -9330,712 +9117,22 @@
         <v>23330051920148</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920117</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330061460223</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920119</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920120</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920121</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920124</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920125</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920126</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920127</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920128</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920129</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920130</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920133</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920134</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920135</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920137</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920122</v>
-      </c>
-      <c r="B26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920140</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920139</v>
-      </c>
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920138</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" t="s">
-        <v>155</v>
-      </c>
-      <c r="E29" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920255</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>124</v>
-      </c>
-      <c r="D30" t="s">
-        <v>156</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>65</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920141</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>23330051920315</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" t="s">
-        <v>158</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>23330051920143</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" t="s">
-        <v>159</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23330051920145</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" t="s">
-        <v>103</v>
-      </c>
-      <c r="D34" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>23330051920146</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" t="s">
-        <v>161</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>23330051920147</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" t="s">
-        <v>162</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>23330051920346</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" t="s">
-        <v>163</v>
-      </c>
-      <c r="E37" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>23330051920149</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" t="s">
-        <v>164</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>23330051920150</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
